--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
   </si>
   <si>
     <t>ТубаКаз1</t>
@@ -113,8 +110,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -200,11 +198,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -212,9 +211,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,20 +567,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>11.052</v>
@@ -599,7 +598,7 @@
         <v>16.91</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -609,20 +608,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2">
+        <v>46149</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>31.482</v>
@@ -640,7 +639,7 @@
         <v>26.13</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -650,103 +649,103 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6">
         <v>31.482</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <v>0.8202</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="6">
         <v>25.82</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="6">
         <v>26.13</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>0.31</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="6">
         <v>11.052</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <v>1.5002</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="6">
         <v>16.58</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>16.91</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>0.33</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="A10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="8">
         <v>42.534</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>2</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <v>42.4</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>43.04</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>0.64</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -146,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,12 +156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -212,17 +206,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,49 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>В7229ВР</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>ТубаКаз1</t>
   </si>
   <si>
-    <t>78970155027722564</t>
-  </si>
-  <si>
     <t>78970155027722572</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:03:00</t>
-  </si>
-  <si>
-    <t>10:57:00</t>
-  </si>
-  <si>
-    <t>3232431938 3232431938</t>
-  </si>
-  <si>
-    <t>3232432214 3232432214</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
@@ -511,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +487,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,195 +528,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>11.33</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>17.45</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>17.79</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>25.63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2">
-        <v>0.77</v>
-      </c>
-      <c r="I2" s="1">
-        <v>19.74</v>
-      </c>
-      <c r="J2">
-        <v>0.78</v>
-      </c>
-      <c r="K2" s="1">
-        <v>19.99</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>119039</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
+      <c r="B7" s="7">
+        <v>11.33</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1.5402</v>
+      </c>
+      <c r="E7" s="7">
+        <v>17.45</v>
+      </c>
+      <c r="F7" s="7">
+        <v>17.79</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>10.52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>16.2</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>16.52</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7">
-        <v>25.63</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="B8" s="10">
+        <v>11.33</v>
+      </c>
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
-        <v>0.7702</v>
-      </c>
-      <c r="E8" s="7">
-        <v>19.74</v>
-      </c>
-      <c r="F8" s="7">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7">
-        <v>10.52</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.5399</v>
-      </c>
-      <c r="E9" s="7">
-        <v>16.2</v>
-      </c>
-      <c r="F9" s="7">
-        <v>16.52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="10">
-        <v>36.15</v>
-      </c>
-      <c r="C10" s="10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>35.94</v>
-      </c>
-      <c r="F10" s="10">
-        <v>36.51</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>17.45</v>
+      </c>
+      <c r="F8" s="10">
+        <v>17.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>12:21</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
@@ -478,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,10 +500,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -528,22 +539,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46178</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>11.33</v>
@@ -560,13 +577,19 @@
       <c r="J2">
         <v>17.79</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
+      <c r="M2">
+        <v>215195</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -574,18 +597,18 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>7</v>
@@ -594,9 +617,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>11.33</v>
@@ -614,9 +637,9 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>11.33</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,31 +55,49 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>В7229ВР</t>
   </si>
   <si>
     <t>ТубаКаз1</t>
   </si>
   <si>
-    <t>В7229ВР</t>
+    <t>78970155027722564</t>
   </si>
   <si>
     <t>78970155027722572</t>
   </si>
   <si>
-    <t>78970155027722564</t>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>2026-07-03 15:01:08</t>
-  </si>
-  <si>
-    <t>2026-07-03 15:09:19</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:49:00</t>
+  </si>
+  <si>
+    <t>14:09:00</t>
+  </si>
+  <si>
+    <t>11:23:00</t>
+  </si>
+  <si>
+    <t>3234894061 3234894061</t>
+  </si>
+  <si>
+    <t>3234951195 3234951195</t>
+  </si>
+  <si>
+    <t>3235487503 3235487503</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
@@ -496,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,15 +526,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -550,174 +573,236 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46206</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>32.44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20.11</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>20.44</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>10.54</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>15.49</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>15.81</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>19.87</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>1.48</v>
+      </c>
+      <c r="I3" s="1">
+        <v>29.41</v>
+      </c>
+      <c r="J3">
+        <v>1.51</v>
+      </c>
+      <c r="K3" s="1">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>10.23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>1.53</v>
+      </c>
+      <c r="I4" s="1">
+        <v>15.65</v>
+      </c>
+      <c r="J4">
+        <v>1.56</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15.96</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46206</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>30.56</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="H3">
-        <v>19.25</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="J3">
-        <v>19.56</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
-        <v>30.56</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.6299</v>
-      </c>
-      <c r="E8" s="7">
-        <v>19.25</v>
-      </c>
-      <c r="F8" s="7">
-        <v>19.56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="B9" s="7">
-        <v>10.54</v>
+        <v>32.44</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
       </c>
       <c r="D9" s="8">
-        <v>1.4696</v>
+        <v>0.6199</v>
       </c>
       <c r="E9" s="7">
-        <v>15.49</v>
+        <v>20.11</v>
       </c>
       <c r="F9" s="7">
-        <v>15.81</v>
+        <v>20.44</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="10">
-        <v>41.1</v>
-      </c>
-      <c r="C10" s="10">
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="C10" s="7">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>34.74</v>
-      </c>
-      <c r="F10" s="10">
-        <v>35.37</v>
+      <c r="D10" s="8">
+        <v>1.497</v>
+      </c>
+      <c r="E10" s="7">
+        <v>45.06</v>
+      </c>
+      <c r="F10" s="7">
+        <v>45.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="10">
+        <v>62.54</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>65.17</v>
+      </c>
+      <c r="F11" s="10">
+        <v>66.40000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -125,7 +125,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="8">
-        <v>0.6199</v>
+        <v>0.619914</v>
       </c>
       <c r="E9" s="7">
         <v>20.11</v>
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.497</v>
+        <v>1.49701</v>
       </c>
       <c r="E10" s="7">
         <v>45.06</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -517,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,13 +533,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,142 +582,154 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>32.44</v>
+        <v>32.444</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
-        <v>20.11</v>
-      </c>
       <c r="J2">
+        <v>20.11528</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
-        <v>20.44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>20.43972</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>25</v>
+      <c r="O2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>19.87</v>
+        <v>19.868</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
+        <v>1.369</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.48</v>
       </c>
-      <c r="I3" s="1">
-        <v>29.41</v>
-      </c>
       <c r="J3">
+        <v>29.40464</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.51</v>
       </c>
-      <c r="K3" s="1">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>30.00068</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>26</v>
+      <c r="O3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>10.23</v>
+        <v>10.231</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4">
+        <v>1.441</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.53</v>
       </c>
-      <c r="I4" s="1">
-        <v>15.65</v>
-      </c>
       <c r="J4">
+        <v>15.65343</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.56</v>
       </c>
-      <c r="K4" s="1">
-        <v>15.96</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>15.96036</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>27</v>
+      <c r="O4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -722,58 +737,58 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
-        <v>32.44</v>
+        <v>32.444</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
       </c>
       <c r="D9" s="8">
-        <v>0.619914</v>
+        <v>0.62</v>
       </c>
       <c r="E9" s="7">
-        <v>20.11</v>
+        <v>20.12</v>
       </c>
       <c r="F9" s="7">
         <v>20.44</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7">
-        <v>30.1</v>
+        <v>30.099</v>
       </c>
       <c r="C10" s="7">
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.49701</v>
+        <v>1.496996</v>
       </c>
       <c r="E10" s="7">
         <v>45.06</v>
@@ -782,19 +797,19 @@
         <v>45.96</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="10">
-        <v>62.54</v>
+        <v>62.543</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>65.17</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="F11" s="10">
         <v>66.40000000000001</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -126,9 +123,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -222,10 +219,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,13 +530,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,154 +579,142 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>32.444</v>
       </c>
       <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20.115</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>20.44</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>20.11528</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>20.43972</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>26</v>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>19.868</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I3" s="1">
-        <v>1.48</v>
+        <v>29.405</v>
       </c>
       <c r="J3">
-        <v>29.40464</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
-        <v>30.00068</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3">
+        <v>30.001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>27</v>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>10.231</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I4" s="1">
-        <v>1.53</v>
+        <v>15.653</v>
       </c>
       <c r="J4">
-        <v>15.65343</v>
+        <v>1.56</v>
       </c>
       <c r="K4" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L4" s="1">
-        <v>15.96036</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4">
+        <v>15.96</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -737,69 +722,69 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>32.444</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>1</v>
       </c>
       <c r="D9" s="8">
         <v>0.62</v>
       </c>
-      <c r="E9" s="7">
-        <v>20.12</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="8">
+        <v>20.115</v>
+      </c>
+      <c r="F9" s="8">
         <v>20.44</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7">
         <v>30.099</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.496996</v>
-      </c>
-      <c r="E10" s="7">
-        <v>45.06</v>
-      </c>
-      <c r="F10" s="7">
-        <v>45.96</v>
+        <v>1.497</v>
+      </c>
+      <c r="E10" s="8">
+        <v>45.058</v>
+      </c>
+      <c r="F10" s="8">
+        <v>45.961</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="10">
         <v>62.543</v>
@@ -809,10 +794,10 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>65.18000000000001</v>
+        <v>65.173</v>
       </c>
       <c r="F11" s="10">
-        <v>66.40000000000001</v>
+        <v>66.401</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,46 +55,19 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В7229ВР</t>
   </si>
   <si>
-    <t>ТубаКаз1</t>
-  </si>
-  <si>
     <t>78970155027722564</t>
   </si>
   <si>
-    <t>78970155027722572</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>15:49:00</t>
-  </si>
-  <si>
-    <t>14:09:00</t>
-  </si>
-  <si>
-    <t>11:23:00</t>
-  </si>
-  <si>
-    <t>3234894061 3234894061</t>
-  </si>
-  <si>
-    <t>3234951195 3234951195</t>
-  </si>
-  <si>
-    <t>3235487503 3235487503</t>
+    <t>10:55</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
@@ -123,9 +93,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -219,10 +189,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -526,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,233 +545,119 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>31.877</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H2">
+        <v>20.401</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="J2">
+        <v>20.72</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>241614</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>32.444</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>0.62</v>
-      </c>
-      <c r="I2" s="1">
-        <v>20.115</v>
-      </c>
-      <c r="J2">
-        <v>0.63</v>
-      </c>
-      <c r="K2" s="1">
-        <v>20.44</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>19.868</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1.48</v>
-      </c>
-      <c r="I3" s="1">
-        <v>29.405</v>
-      </c>
-      <c r="J3">
-        <v>1.51</v>
-      </c>
-      <c r="K3" s="1">
-        <v>30.001</v>
-      </c>
-      <c r="L3" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7">
+        <v>31.877</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.6399899999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>20.4</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20.72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>10.231</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>1.53</v>
-      </c>
-      <c r="I4" s="1">
-        <v>15.653</v>
-      </c>
-      <c r="J4">
-        <v>1.56</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15.96</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>32.444</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B8" s="10">
+        <v>31.877</v>
+      </c>
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D9" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="E9" s="8">
-        <v>20.115</v>
-      </c>
-      <c r="F9" s="8">
-        <v>20.44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="7">
-        <v>30.099</v>
-      </c>
-      <c r="C10" s="8">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.497</v>
-      </c>
-      <c r="E10" s="8">
-        <v>45.058</v>
-      </c>
-      <c r="F10" s="8">
-        <v>45.961</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="10">
-        <v>62.543</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>65.173</v>
-      </c>
-      <c r="F11" s="10">
-        <v>66.401</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>20.4</v>
+      </c>
+      <c r="F8" s="10">
+        <v>20.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,7 +58,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В7229ВР</t>
@@ -67,7 +70,22 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>10:55</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>11:27:00</t>
+  </si>
+  <si>
+    <t>3236662972 3236662972</t>
+  </si>
+  <si>
+    <t>3236663388 3236663388</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО</t>
@@ -92,10 +110,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -175,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -189,10 +208,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -496,16 +517,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,119 +567,189 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>31.27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="1">
+        <v>30.957</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>20.638</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>31.877</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H2">
-        <v>20.401</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>20.72</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>19.11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I3" s="1">
+        <v>27.308</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>30.003</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>241614</v>
+      <c r="B8" s="7">
+        <v>31.27</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.98999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>30.96</v>
+      </c>
+      <c r="F8" s="7">
+        <v>20.64</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="B9" s="7">
+        <v>19.11</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1.42899</v>
+      </c>
+      <c r="E9" s="7">
+        <v>27.31</v>
+      </c>
+      <c r="F9" s="7">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7">
-        <v>31.877</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.6399899999999999</v>
-      </c>
-      <c r="E7" s="7">
-        <v>20.4</v>
-      </c>
-      <c r="F7" s="7">
-        <v>20.72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="10">
-        <v>31.877</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>20.4</v>
-      </c>
-      <c r="F8" s="10">
-        <v>20.72</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="11">
+        <v>50.38</v>
+      </c>
+      <c r="C10" s="12">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="11">
+        <v>58.27</v>
+      </c>
+      <c r="F10" s="11">
+        <v>50.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО/ОБЩИНА ВАРНА - КМЕТСТВО КАЗАШКО.xlsx
@@ -594,10 +594,10 @@
         <v>19</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>30.957</v>
+        <v>20.326</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -638,10 +638,10 @@
         <v>19</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I3" s="1">
-        <v>27.308</v>
+        <v>29.429</v>
       </c>
       <c r="J3" s="1">
         <v>1.57</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="9">
-        <v>0.98999</v>
+        <v>0.65002</v>
       </c>
       <c r="E8" s="7">
-        <v>30.96</v>
+        <v>20.33</v>
       </c>
       <c r="F8" s="7">
         <v>20.64</v>
@@ -720,10 +720,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="9">
-        <v>1.42899</v>
+        <v>1.53998</v>
       </c>
       <c r="E9" s="7">
-        <v>27.31</v>
+        <v>29.43</v>
       </c>
       <c r="F9" s="7">
         <v>30</v>
@@ -741,7 +741,7 @@
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="11">
-        <v>58.27</v>
+        <v>49.76</v>
       </c>
       <c r="F10" s="11">
         <v>50.64</v>
